--- a/data/trans_dic/P55$auxiliar-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P55$auxiliar-Estudios-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que, al menos, le ayuda los Servicios Sociales cuando tiene dificultades en la actividades instrumentales</t>
+          <t>Población a la que, al menos, le ayuda los Servicios Sociales cuando tiene dificultades en la actividades instrumentales (tasa de respuesta: 98,48%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,71</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,44; 14,54</t>
+          <t>4,41; 15,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,63; 12,01</t>
+          <t>2,74; 12,91</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>16,04; 29,6</t>
+          <t>16,3; 30,43</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,35; 8,25</t>
+          <t>2,12; 8,38</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>15,42; 25,65</t>
+          <t>15,99; 26,0</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,57; 12,66</t>
+          <t>4,43; 12,8</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>21,86; 29,69</t>
+          <t>22,39; 29,82</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,68; 5,91</t>
+          <t>1,39; 5,5</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>13,05; 20,7</t>
+          <t>13,19; 20,79</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4,58; 10,65</t>
+          <t>4,54; 11,35</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>21,47; 28,32</t>
+          <t>21,72; 28,26</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,84</t>
+          <t>0,0; 26,05</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,31</t>
+          <t>0,0; 22,91</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0; 7,06</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7,72; 25,26</t>
+          <t>7,8; 24,42</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0; 14,51</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0; 9,99</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,77</t>
+          <t>0,0; 11,76</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>15,52; 31,64</t>
+          <t>16,28; 32,37</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,68</t>
+          <t>0,0; 15,6</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,13</t>
+          <t>0,0; 11,25</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,06</t>
+          <t>0,0; 6,65</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>13,82; 25,56</t>
+          <t>13,95; 25,7</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 23,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 56,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 30,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 7,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 15,69</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 36,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 30,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,92; 34,6</t>
+          <t>2,72; 33,28</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 9,99</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0; 26,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 17,08</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,36; 18,75</t>
+          <t>1,32; 18,51</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,64</t>
+          <t>0,0; 3,59</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,28; 14,05</t>
+          <t>4,21; 13,99</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,08; 9,95</t>
+          <t>2,01; 9,49</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>13,81; 23,04</t>
+          <t>13,8; 23,48</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,87; 7,42</t>
+          <t>1,91; 7,67</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>14,48; 24,29</t>
+          <t>14,45; 23,46</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,77; 10,54</t>
+          <t>3,81; 10,86</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>21,85; 28,41</t>
+          <t>21,53; 28,2</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,62; 5,47</t>
+          <t>1,51; 5,32</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>11,52; 18,67</t>
+          <t>11,71; 18,82</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3,86; 9,25</t>
+          <t>3,7; 8,66</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>19,81; 25,45</t>
+          <t>20,03; 25,43</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que, al menos, le ayuda los Servicios Sociales cuando tiene dificultades en la actividades instrumentales</t>
+          <t>Población a la que, al menos, le ayuda los Servicios Sociales cuando tiene dificultades en la actividades instrumentales (tasa de respuesta: 98,48%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 1763</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>5510; 18047</t>
+          <t>5471; 18623</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2458; 11225</t>
+          <t>2565; 12069</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>15664; 28902</t>
+          <t>15919; 29714</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>4835; 16992</t>
+          <t>4361; 17258</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>38682; 64330</t>
+          <t>40105; 65218</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>9528; 26403</t>
+          <t>9247; 26696</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>56331; 76497</t>
+          <t>57690; 76841</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>5186; 18258</t>
+          <t>4282; 16989</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>48932; 77630</t>
+          <t>49445; 77941</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>13834; 32154</t>
+          <t>13698; 34295</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>76278; 100645</t>
+          <t>77180; 100427</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 3666</t>
+          <t>0; 3696</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 4266</t>
+          <t>0; 4585</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 1614</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3320; 10867</t>
+          <t>3357; 10504</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 1958</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 2113</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 5082</t>
+          <t>0; 6119</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8484; 17296</t>
+          <t>8898; 17691</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 4341</t>
+          <t>0; 4318</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0; 4993</t>
+          <t>0; 4631</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 6038</t>
+          <t>0; 4979</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>13500; 24971</t>
+          <t>13627; 25109</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 2177</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 1154</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 1565</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 1151</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 1815</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 1603</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 2067</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>408; 4840</t>
+          <t>381; 4655</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 2091</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>0; 1704</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0; 2029</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>395; 5458</t>
+          <t>384; 5387</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 4607</t>
+          <t>0; 4547</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6250; 20530</t>
+          <t>6158; 20445</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2529; 12082</t>
+          <t>2442; 11524</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>21514; 35899</t>
+          <t>21500; 36585</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>4324; 17142</t>
+          <t>4420; 17722</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>40036; 67156</t>
+          <t>39938; 64841</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>10079; 28185</t>
+          <t>10177; 29027</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>71295; 92708</t>
+          <t>70253; 92006</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>5776; 19551</t>
+          <t>5392; 19014</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>48667; 78905</t>
+          <t>49482; 79548</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>15005; 35978</t>
+          <t>14368; 33654</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>95499; 122702</t>
+          <t>96552; 122602</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P55$auxiliar-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P55$auxiliar-Estudios-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>22,65%</t>
+          <t>22,59%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>25,77%</t>
+          <t>25,55%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>24,91%</t>
+          <t>24,75%</t>
         </is>
       </c>
     </row>
@@ -722,57 +722,57 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,41; 15,0</t>
+          <t>4,37; 14,82</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,74; 12,91</t>
+          <t>2,68; 12,55</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>16,3; 30,43</t>
+          <t>16,45; 29,57</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,12; 8,38</t>
+          <t>2,1; 8,57</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>15,99; 26,0</t>
+          <t>15,6; 26,6</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,43; 12,8</t>
+          <t>4,28; 12,23</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>22,39; 29,82</t>
+          <t>22,06; 29,88</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,39; 5,5</t>
+          <t>1,62; 5,68</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>13,19; 20,79</t>
+          <t>13,39; 20,72</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4,54; 11,35</t>
+          <t>4,61; 11,23</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>21,72; 28,26</t>
+          <t>21,55; 28,0</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>22,93%</t>
+          <t>22,9%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>19,42%</t>
+          <t>19,68%</t>
         </is>
       </c>
     </row>
@@ -857,12 +857,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,05</t>
+          <t>0,0; 25,77</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,91</t>
+          <t>0,0; 23,97</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7,8; 24,42</t>
+          <t>8,68; 24,54</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -887,32 +887,32 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,76</t>
+          <t>0,0; 9,68</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>16,28; 32,37</t>
+          <t>14,6; 31,17</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,6</t>
+          <t>0,0; 18,06</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,25</t>
+          <t>0,0; 12,43</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,65</t>
+          <t>0,0; 8,92</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>13,95; 25,7</t>
+          <t>14,23; 25,95</t>
         </is>
       </c>
     </row>
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>5,45%</t>
         </is>
       </c>
     </row>
@@ -1032,7 +1032,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,72; 33,28</t>
+          <t>2,48; 28,81</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1052,7 +1052,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,32; 18,51</t>
+          <t>1,24; 15,9</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>18,33%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>24,75%</t>
+          <t>24,45%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>22,67%</t>
+          <t>22,49%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,59</t>
+          <t>0,0; 3,37</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,21; 13,99</t>
+          <t>4,38; 13,59</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,01; 9,49</t>
+          <t>2,0; 9,63</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>13,8; 23,48</t>
+          <t>13,82; 23,84</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,91; 7,67</t>
+          <t>1,99; 7,38</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>14,45; 23,46</t>
+          <t>14,0; 23,38</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,81; 10,86</t>
+          <t>3,71; 10,81</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>21,53; 28,2</t>
+          <t>20,99; 27,7</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,51; 5,32</t>
+          <t>1,31; 5,09</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>11,71; 18,82</t>
+          <t>11,96; 18,71</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3,7; 8,66</t>
+          <t>3,81; 9,16</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>20,03; 25,43</t>
+          <t>19,66; 25,28</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>22114</t>
+          <t>23440</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>66407</t>
+          <t>70737</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>88521</t>
+          <t>94177</t>
         </is>
       </c>
     </row>
@@ -1509,57 +1509,57 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>5471; 18623</t>
+          <t>5418; 18395</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2565; 12069</t>
+          <t>2504; 11732</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>15919; 29714</t>
+          <t>17075; 30688</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>4361; 17258</t>
+          <t>4322; 17647</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>40105; 65218</t>
+          <t>39142; 66735</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>9247; 26696</t>
+          <t>8932; 25514</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>57690; 76841</t>
+          <t>61068; 82717</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>4282; 16989</t>
+          <t>4989; 17532</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>49445; 77941</t>
+          <t>50209; 77692</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>13698; 34295</t>
+          <t>13931; 33905</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>77180; 100427</t>
+          <t>82014; 106568</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6433</t>
+          <t>7296</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>12532</t>
+          <t>14349</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>18966</t>
+          <t>21645</t>
         </is>
       </c>
     </row>
@@ -1712,12 +1712,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 3696</t>
+          <t>0; 3656</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 4585</t>
+          <t>0; 4798</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1727,7 +1727,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3357; 10504</t>
+          <t>4108; 11612</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1742,32 +1742,32 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 6119</t>
+          <t>0; 5037</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8898; 17691</t>
+          <t>9150; 19532</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 4318</t>
+          <t>0; 5001</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0; 4631</t>
+          <t>0; 5119</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 4979</t>
+          <t>0; 6681</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>13627; 25109</t>
+          <t>15649; 28541</t>
         </is>
       </c>
     </row>
@@ -1887,7 +1887,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1813</t>
+          <t>1762</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1813</t>
+          <t>1762</t>
         </is>
       </c>
     </row>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>381; 4655</t>
+          <t>390; 4535</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1975,7 +1975,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>384; 5387</t>
+          <t>401; 5137</t>
         </is>
       </c>
     </row>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>28548</t>
+          <t>30736</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>80752</t>
+          <t>86848</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>109300</t>
+          <t>117584</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 4547</t>
+          <t>0; 4266</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6158; 20445</t>
+          <t>6405; 19858</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2442; 11524</t>
+          <t>2430; 11702</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>21500; 36585</t>
+          <t>23172; 39978</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>4420; 17722</t>
+          <t>4599; 17041</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>39938; 64841</t>
+          <t>38690; 64638</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>10177; 29027</t>
+          <t>9908; 28902</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>70253; 92006</t>
+          <t>74542; 98379</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>5392; 19014</t>
+          <t>4675; 18213</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>49482; 79548</t>
+          <t>50526; 79053</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>14368; 33654</t>
+          <t>14812; 35603</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>96552; 122602</t>
+          <t>102813; 132195</t>
         </is>
       </c>
     </row>
